--- a/monitor-zentao/code/nocodebug.xlsx
+++ b/monitor-zentao/code/nocodebug.xlsx
@@ -448,7 +448,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="31" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>42394</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -568,12 +568,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>EPM20.2</t>
+          <t>其它</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>关于断网情况下活动入口没有保持上一次状态问题</t>
+          <t>关于AD Brand以外AD版本依然显示了活动条的问题</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -593,22 +593,22 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28 13:14:15</t>
+          <t>2026-05-08 11:29:36</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>韦家鹏</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28 13:16:51</t>
+          <t>2026-05-08 13:49:21</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -618,12 +618,12 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28 13:16:10</t>
+          <t>2026-05-08 13:48:53</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>bydesign</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr"/>

--- a/monitor-zentao/code/nocodebug.xlsx
+++ b/monitor-zentao/code/nocodebug.xlsx
@@ -441,14 +441,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -458,7 +458,7 @@
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
   </cols>
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>42412</t>
+          <t>42481</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -563,17 +563,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EPM20.2.0</t>
+          <t>EPM20.5.0</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>其它</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>关于AD Brand以外AD版本依然显示了活动条的问题</t>
+          <t>关于Discovery页本地ECG安装不成功问题</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -593,41 +593,456 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 11:29:36</t>
+          <t>2026-05-19 14:34:08</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 13:49:21</t>
+          <t>2026-05-19 15:00:25</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>彭均</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 13:48:53</t>
+          <t>2026-05-19 15:00:20</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>42470</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.5</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>关于同一路径Space Analyze扫描出来的数据是不一样的</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15 10:56:10</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:22:10</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>谢蜀岷</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18 13:19:41</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:22:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>42421</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>空间管理</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>关于Clean页面，多次点击调用Space Analysis，会蓝屏的问题</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:05:19</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18 10:14:11</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>谢蜀岷</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18 10:13:33</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>42461</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>空间管理</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>当ECG清理完成后点击关闭时，有可能导致系统崩溃</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>刘冬</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13 14:15:59</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>邓贵星</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18 10:15:04</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>谢蜀岷</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18 10:05:21</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>notrepro</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>42435</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>空间管理</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>关于EPM Clean页面，Space Analysis显示数据不会刷新的问题</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 15:33:39</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>贺照云</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15 16:15:36</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>余悦</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15 15:38:38</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>nonproblem</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>42467</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>空间管理</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>关于Clean-空间分析，没有屏蔽网络映射和exFAT的问题</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15 10:05:28</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>贺照云</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15 16:14:24</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>余悦</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15 10:46:06</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>bydesign</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0000-00-00 00:00:00</t>
         </is>

--- a/monitor-zentao/code/nocodebug.xlsx
+++ b/monitor-zentao/code/nocodebug.xlsx
@@ -441,14 +441,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -458,7 +458,7 @@
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
   </cols>
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>42481</t>
+          <t>42483</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>关于Discovery页本地ECG安装不成功问题</t>
+          <t>关于clean页面调用出了本地ecg程序问题</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 14:34:08</t>
+          <t>2026-05-21 08:55:22</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 15:00:25</t>
+          <t>2026-05-21 10:55:55</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -618,431 +618,16 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 15:00:20</t>
+          <t>2026-05-21 10:53:50</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>0000-00-00 00:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>42470</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>EPM</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>EPM20.5.0</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>EPM20.5</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>关于同一路径Space Analyze扫描出来的数据是不一样的</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>辜健</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-15 10:56:10</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-19 17:22:10</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>谢蜀岷</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18 13:19:41</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>duplicate</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>辜健</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-19 17:22:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>42421</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>EPM</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>EPM20.5.0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>空间管理</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>关于Clean页面，多次点击调用Space Analysis，会蓝屏的问题</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>resolved</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>何峻</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-09 11:05:19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>何峻</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18 10:14:11</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>谢蜀岷</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18 10:13:33</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>duplicate</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0000-00-00 00:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>42461</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>EPM</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>EPM20.5.0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>空间管理</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>当ECG清理完成后点击关闭时，有可能导致系统崩溃</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>resolved</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>刘冬</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-13 14:15:59</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>邓贵星</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18 10:15:04</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>谢蜀岷</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18 10:05:21</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>notrepro</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0000-00-00 00:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>42435</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>EPM</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>EPM20.5.0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>空间管理</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>关于EPM Clean页面，Space Analysis显示数据不会刷新的问题</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>resolved</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>何峻</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-09 15:33:39</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>贺照云</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-15 16:15:36</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>余悦</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-15 15:38:38</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>nonproblem</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>0000-00-00 00:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>42467</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>EPM</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>EPM20.5.0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>空间管理</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>关于Clean-空间分析，没有屏蔽网络映射和exFAT的问题</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>resolved</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>何峻</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-15 10:05:28</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>贺照云</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-15 16:14:24</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>余悦</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-15 10:46:06</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>bydesign</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0000-00-00 00:00:00</t>
         </is>
